--- a/claimit_bulk_template_28.xlsx
+++ b/claimit_bulk_template_28.xlsx
@@ -817,7 +817,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid category" error="Please pick a category from the dropdown list." promptTitle="Category" prompt="Click the arrow and pick one category." type="list">
+    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Category" prompt="Pick one from the dropdown (you can also paste / fill down)." type="list">
       <formula1>$AA$1:$AA$28</formula1>
     </dataValidation>
   </dataValidations>
